--- a/artfynd/A 62054-2021 artfynd.xlsx
+++ b/artfynd/A 62054-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62054-2021 artfynd.xlsx
+++ b/artfynd/A 62054-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97254841</v>
+        <v>112044152</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554715.3061975719</v>
+        <v>554746</v>
       </c>
       <c r="R2" t="n">
-        <v>6697471.953922784</v>
+        <v>6697510</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,73 +760,58 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97256913</v>
+        <v>96418265</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554676.9304097352</v>
+        <v>554743</v>
       </c>
       <c r="R3" t="n">
-        <v>6697489.657601082</v>
+        <v>6697536</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,22 +838,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,73 +868,58 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97254818</v>
+        <v>97329988</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554694.4943768198</v>
+        <v>554740</v>
       </c>
       <c r="R4" t="n">
-        <v>6697473.616651565</v>
+        <v>6697466</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,22 +946,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,49 +976,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97329988</v>
+        <v>97329978</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1085,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554740.6309467416</v>
+        <v>554718</v>
       </c>
       <c r="R5" t="n">
-        <v>6697466.406488007</v>
+        <v>6697443</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1120,7 +1059,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1069,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,53 +1096,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112044152</v>
+        <v>96418252</v>
       </c>
       <c r="B6" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554746</v>
+        <v>554743</v>
       </c>
       <c r="R6" t="n">
-        <v>6697510</v>
+        <v>6697536</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,12 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97255460</v>
+        <v>97123388</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1310,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554812.5203313293</v>
+        <v>554692</v>
       </c>
       <c r="R7" t="n">
-        <v>6697458.103415021</v>
+        <v>6697450</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,22 +1281,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,27 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97255637</v>
+        <v>97254543</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1353,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1433,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554812.0055166895</v>
+        <v>554692</v>
       </c>
       <c r="R8" t="n">
-        <v>6697492.189299049</v>
+        <v>6697438</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,27 +1429,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97255587</v>
+        <v>97254703</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554799.2001886531</v>
+        <v>554702</v>
       </c>
       <c r="R9" t="n">
-        <v>6697488.043045225</v>
+        <v>6697440</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1591,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,15 +1547,959 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97254818</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>554694</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6697474</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97254841</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>554716</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6697472</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97255460</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>554813</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6697459</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>97255587</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>554799</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6697489</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97255637</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>554813</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6697492</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>97255723</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>554753</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6697536</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>97256913</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>554677</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6697490</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-11-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>97311602</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>554765</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6697529</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62054-2021 artfynd.xlsx
+++ b/artfynd/A 62054-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112044152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96418265</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329988</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329978</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96418252</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97123388</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97254543</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97254703</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97254818</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97254841</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1910,6 +1965,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97255460</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2028,6 +2088,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97255587</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2146,6 +2211,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97255637</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2264,6 +2334,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97255723</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2382,6 +2457,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97256913</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2500,8 +2580,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97311602</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>